--- a/Input/Takaful_Mednet/benefits.xlsx
+++ b/Input/Takaful_Mednet/benefits.xlsx
@@ -312,35 +312,19 @@
     <t xml:space="preserve">Yes</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Consultation 20% with AED 50 max,all other OP nil</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/Nil/Nil</t>
-    </r>
+    <t xml:space="preserve">Consultation 20% with AED 50 max,all other OP nil/Nil/Nil</t>
   </si>
   <si>
     <t xml:space="preserve">takaful_emarat_mednet</t>
   </si>
   <si>
-    <t xml:space="preserve">UAE</t>
+    <t xml:space="preserve">AE - AU </t>
   </si>
   <si>
     <t xml:space="preserve">2023-04-01</t>
   </si>
   <si>
-    <t xml:space="preserve">USA</t>
+    <t xml:space="preserve">AbuDhabi</t>
   </si>
   <si>
     <t xml:space="preserve">Annually</t>
@@ -352,23 +336,7 @@
     <t xml:space="preserve">Mednet Silver Classic</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Consultation 20% with AED 50 max,all other OP 10%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/10/10</t>
-    </r>
+    <t xml:space="preserve">Consultation 20% with AED 50 max,all other OP 10%/10/10</t>
   </si>
   <si>
     <t xml:space="preserve">Iridium</t>
@@ -377,23 +345,7 @@
     <t xml:space="preserve">Mednet Green</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Consultation 20% with AED 50 max, all other OP 20%</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/20/20</t>
-    </r>
+    <t xml:space="preserve">Consultation 20% with AED 50 max, all other OP 20%/20/20</t>
   </si>
   <si>
     <t xml:space="preserve">Platinum</t>
@@ -422,7 +374,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="@"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="7">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -462,11 +414,6 @@
       <name val="Times New Roman"/>
       <family val="1"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -536,7 +483,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
